--- a/data/trans_orig/P21D3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D3_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir algún medicamento en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir algún medicamento en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42735</t>
+          <t>42840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72556</t>
+          <t>72177</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43975</t>
+          <t>43716</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67802</t>
+          <t>65467</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92395</t>
+          <t>92620</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>130227</t>
+          <t>132381</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>151401</t>
+          <t>151457</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>181294</t>
+          <t>180848</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146945</t>
+          <t>149982</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>171836</t>
+          <t>171607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>308268</t>
+          <t>307883</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>347344</t>
+          <t>346217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9632</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32977</t>
+          <t>34147</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57899</t>
+          <t>57957</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28568</t>
+          <t>28098</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>48453</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66607</t>
+          <t>67950</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>98252</t>
+          <t>98112</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123171</t>
+          <t>122872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147852</t>
+          <t>146643</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127768</t>
+          <t>127923</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>148245</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259357</t>
+          <t>259803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>291106</t>
+          <t>290077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,64%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>585</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>5433</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1638,97 +1638,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1787</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>1492</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14180</t>
+          <t>12802</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123385</t>
+          <t>126633</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17763</t>
+          <t>18469</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19292</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123788</t>
+          <t>124867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>368034</t>
+          <t>368033</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>291811</t>
+          <t>288562</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>401016</t>
+          <t>402393</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>59620</t>
+          <t>59583</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70503</t>
+          <t>70981</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>368322</t>
+          <t>366990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>474468</t>
+          <t>478350</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -2094,97 +2094,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1132</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4193</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1132</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3970</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4560</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1132</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4647</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2207,97 +2207,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4193</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2973</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>115397</t>
+          <t>114209</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>156411</t>
+          <t>158091</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52306</t>
+          <t>52139</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78793</t>
+          <t>79061</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>175343</t>
+          <t>174573</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>226169</t>
+          <t>225067</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292880</t>
+          <t>291497</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>334862</t>
+          <t>335408</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254861</t>
+          <t>254678</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>282324</t>
+          <t>283016</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>558322</t>
+          <t>559041</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>609372</t>
+          <t>609394</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8809</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>17319</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -2776,97 +2776,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1765</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3507</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3835</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3983</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3485</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50019</t>
+          <t>49681</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>80957</t>
+          <t>80419</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54317</t>
+          <t>53772</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>257635</t>
+          <t>235102</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>119517</t>
+          <t>117935</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>309997</t>
+          <t>318943</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>140252</t>
+          <t>140303</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>171790</t>
+          <t>171190</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>155947</t>
+          <t>179422</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>358993</t>
+          <t>358501</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>324781</t>
+          <t>307399</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>515354</t>
+          <t>516253</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>347</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>346</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>539</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29119</t>
+          <t>27752</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>62725</t>
+          <t>63679</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>63808</t>
+          <t>63294</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>97660</t>
+          <t>95364</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>100307</t>
+          <t>99137</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>148696</t>
+          <t>148451</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,58%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>60602</t>
+          <t>59648</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>94208</t>
+          <t>95575</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>218973</t>
+          <t>218907</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>251805</t>
+          <t>251092</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>289321</t>
+          <t>289089</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>337692</t>
+          <t>338677</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9789</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3914,97 +3914,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>4140</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>1259</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1566</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>237520</t>
+          <t>242014</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>480107</t>
+          <t>478912</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>300100</t>
+          <t>300473</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>559637</t>
+          <t>582100</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>603927</t>
+          <t>592356</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>906218</t>
+          <t>913137</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1134479</t>
+          <t>1134565</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1385146</t>
+          <t>1375306</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>977123</t>
+          <t>959981</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1232777</t>
+          <t>1233389</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2246970</t>
+          <t>2234427</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2548700</t>
+          <t>2559306</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14656</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>23207</t>
+          <t>22432</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>14659</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>33468</t>
+          <t>33064</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>540</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>746</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D3_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>55580</t>
+          <t>64129</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42840</t>
+          <t>49728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72177</t>
+          <t>81688</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>54471</t>
+          <t>58247</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43716</t>
+          <t>46266</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65467</t>
+          <t>70779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>110051</t>
+          <t>122376</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92620</t>
+          <t>103385</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132381</t>
+          <t>144592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>168109</t>
+          <t>179025</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>151457</t>
+          <t>162043</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>180848</t>
+          <t>193204</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>161115</t>
+          <t>174090</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149982</t>
+          <t>161380</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>171607</t>
+          <t>185758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>329224</t>
+          <t>353115</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>307883</t>
+          <t>331309</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>346217</t>
+          <t>372339</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,22 +1021,22 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44461</t>
+          <t>49245</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34147</t>
+          <t>37572</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57957</t>
+          <t>64105</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37901</t>
+          <t>41655</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28098</t>
+          <t>30688</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48453</t>
+          <t>52054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>82362</t>
+          <t>90900</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>67950</t>
+          <t>75330</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>98112</t>
+          <t>109440</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>136515</t>
+          <t>146892</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122872</t>
+          <t>131952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146643</t>
+          <t>158460</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>138823</t>
+          <t>153655</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127923</t>
+          <t>142853</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>148300</t>
+          <t>165064</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>275338</t>
+          <t>300547</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259803</t>
+          <t>281891</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>290077</t>
+          <t>315702</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>790</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>47162</t>
+          <t>50080</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12802</t>
+          <t>38307</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126633</t>
+          <t>64853</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11760</t>
+          <t>12619</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>58923</t>
+          <t>62699</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15350</t>
+          <t>48999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>124867</t>
+          <t>79282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>368033</t>
+          <t>138757</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>288562</t>
+          <t>123984</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>402393</t>
+          <t>150530</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66060</t>
+          <t>72866</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>66765</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70981</t>
+          <t>77656</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>434093</t>
+          <t>211623</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>366990</t>
+          <t>195008</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>478350</t>
+          <t>224862</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>81,63%</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4242</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>136392</t>
+          <t>157683</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>114209</t>
+          <t>134706</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>158091</t>
+          <t>182999</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>64546</t>
+          <t>71413</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52139</t>
+          <t>58605</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79061</t>
+          <t>86451</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>200938</t>
+          <t>229096</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>174573</t>
+          <t>202410</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>225067</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>314052</t>
+          <t>348457</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291497</t>
+          <t>323999</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>335408</t>
+          <t>371029</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>269671</t>
+          <t>310352</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254678</t>
+          <t>294987</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>283016</t>
+          <t>323418</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>583723</t>
+          <t>658809</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>559041</t>
+          <t>630128</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>609394</t>
+          <t>686469</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,35%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13339</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>17319</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>65328</t>
+          <t>91087</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49681</t>
+          <t>73568</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>80419</t>
+          <t>109540</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>117611</t>
+          <t>60217</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53772</t>
+          <t>49242</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>235102</t>
+          <t>75742</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>182939</t>
+          <t>151305</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>117935</t>
+          <t>131019</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>318943</t>
+          <t>180232</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>156007</t>
+          <t>174173</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>140303</t>
+          <t>155840</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>171190</t>
+          <t>192216</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>295915</t>
+          <t>325665</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>179422</t>
+          <t>309394</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>358501</t>
+          <t>336614</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>451923</t>
+          <t>499838</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>307399</t>
+          <t>470590</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>516253</t>
+          <t>520776</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>370</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>373</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3350,57 +3350,57 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>4713</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>4590</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,22 +3410,22 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>416597</t>
+          <t>389123</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>416597</t>
+          <t>389123</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>416597</t>
+          <t>389123</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>638697</t>
+          <t>655130</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>638697</t>
+          <t>655130</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>638697</t>
+          <t>655130</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>44259</t>
+          <t>48186</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27752</t>
+          <t>32547</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>63679</t>
+          <t>65079</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>78346</t>
+          <t>88599</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>63294</t>
+          <t>71017</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>95364</t>
+          <t>107030</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>122606</t>
+          <t>136785</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>99137</t>
+          <t>114058</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>148451</t>
+          <t>161518</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>79068</t>
+          <t>69251</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>59648</t>
+          <t>52358</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>95575</t>
+          <t>84890</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>236391</t>
+          <t>262102</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>218907</t>
+          <t>243375</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>251092</t>
+          <t>279015</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>315460</t>
+          <t>331353</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>289089</t>
+          <t>306154</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>338677</t>
+          <t>354505</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>13217</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>393183</t>
+          <t>460411</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>242014</t>
+          <t>418421</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>478912</t>
+          <t>503288</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>364636</t>
+          <t>332750</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>300473</t>
+          <t>301707</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>582100</t>
+          <t>362521</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>757819</t>
+          <t>793161</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>592356</t>
+          <t>740157</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>913137</t>
+          <t>847715</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1221784</t>
+          <t>1056556</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1134565</t>
+          <t>1014365</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1375306</t>
+          <t>1098221</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1167976</t>
+          <t>1298729</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>959981</t>
+          <t>1266892</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1233389</t>
+          <t>1330381</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>2389761</t>
+          <t>2355286</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2234427</t>
+          <t>2303920</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2559306</t>
+          <t>2408451</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>75,85%</t>
         </is>
       </c>
     </row>
@@ -4365,27 +4365,27 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>15741</t>
+          <t>14867</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4400,22 +4400,22 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>16183</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>10355</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>22432</t>
+          <t>25612</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>23923</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>33064</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,17 +4518,17 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,17 +4548,17 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>708</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1549615</t>
+          <t>1649675</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1549615</t>
+          <t>1649675</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1549615</t>
+          <t>1649675</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3172850</t>
+          <t>3175129</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3172850</t>
+          <t>3175129</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3172850</t>
+          <t>3175129</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
